--- a/reports/滨江一号_2026-06-21_交接包/滨江一号_2026-06-21_桩基校核报告.xlsx
+++ b/reports/滨江一号_2026-06-21_交接包/滨江一号_2026-06-21_桩基校核报告.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-21 05:26:35</t>
+          <t>2026-06-21 05:43:36</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
